--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513648_FASEFINALAFFA1_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513648_FASEFINALAFFA1_PROCESSED.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>F. MARCO CLIMENT</t>
+          <t>L. CERVANTES GUERRA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7015</v>
+        <v>4.1935</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8609</v>
+        <v>1.7948</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8406</v>
+        <v>2.3987</v>
       </c>
       <c r="G2" t="n">
-        <v>2.829</v>
+        <v>2.7158</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4481</v>
+        <v>1.7837</v>
       </c>
       <c r="I2" t="n">
-        <v>2.3809</v>
+        <v>0.9321</v>
       </c>
       <c r="J2" t="n">
-        <v>4.8854</v>
+        <v>1.7301</v>
       </c>
       <c r="K2" t="n">
-        <v>1.5217</v>
+        <v>2.3863</v>
       </c>
       <c r="L2" t="n">
-        <v>3.3637</v>
+        <v>-0.6561</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.0564</v>
+        <v>0.9857</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.0736</v>
+        <v>-0.6025</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.9828</v>
+        <v>1.5883</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3895</v>
+        <v>0.9737</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1684</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5579</v>
+        <v>0.9737</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2552</v>
+        <v>0.5556</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.08400000000000001</v>
+        <v>0.1163</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3391</v>
+        <v>0.4393</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2279</v>
+        <v>-0.0516</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2279</v>
+        <v>-0.0516</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. CERVANTES GUERRA</t>
+          <t>F. MARCO CLIMENT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4988</v>
+        <v>3.5677</v>
       </c>
       <c r="E3" t="n">
-        <v>1.434</v>
+        <v>3.5619</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0648</v>
+        <v>0.0058</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7158</v>
+        <v>2.829</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7837</v>
+        <v>0.4481</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9321</v>
+        <v>2.3809</v>
       </c>
       <c r="J3" t="n">
-        <v>1.7301</v>
+        <v>4.8854</v>
       </c>
       <c r="K3" t="n">
-        <v>2.3863</v>
+        <v>1.5217</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6561</v>
+        <v>3.3637</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9857</v>
+        <v>-2.0564</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6025</v>
+        <v>-1.0736</v>
       </c>
       <c r="O3" t="n">
-        <v>1.5883</v>
+        <v>-0.9828</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9737</v>
+        <v>0.3895</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.1684</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9737</v>
+        <v>1.5579</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1392</v>
+        <v>0.1214</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2446</v>
+        <v>-0.383</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1054</v>
+        <v>0.5044</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.0516</v>
+        <v>0.2279</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.0516</v>
+        <v>0.2279</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5884</v>
+        <v>1.801</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7785</v>
+        <v>0.7406</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8099</v>
+        <v>1.0603</v>
       </c>
       <c r="G5" t="n">
         <v>1.6114</v>
@@ -844,13 +844,13 @@
         <v>0.3895</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.133</v>
+        <v>0.0796</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0554</v>
+        <v>0.0175</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1884</v>
+        <v>0.0621</v>
       </c>
       <c r="V5" t="n">
         <v>-0.2795</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0952</v>
+        <v>1.4499</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0278</v>
+        <v>0.3269</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0674</v>
+        <v>1.123</v>
       </c>
       <c r="G6" t="n">
         <v>0.6997</v>
@@ -922,13 +922,13 @@
         <v>0.7789</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2998</v>
+        <v>0.0549</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7946</v>
+        <v>-0.4956</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4949</v>
+        <v>0.5505</v>
       </c>
       <c r="V6" t="n">
         <v>0.89</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9510999999999999</v>
+        <v>0.8576</v>
       </c>
       <c r="E7" t="n">
-        <v>0.623</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3281</v>
+        <v>0.2725</v>
       </c>
       <c r="G7" t="n">
         <v>0.2001</v>
@@ -1000,13 +1000,13 @@
         <v>0.1947</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5563</v>
+        <v>0.4628</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2409</v>
+        <v>0.2031</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3154</v>
+        <v>0.2598</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3062</v>
+        <v>-0.6349</v>
       </c>
       <c r="E8" t="n">
-        <v>0.577</v>
+        <v>-0.4198</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2708</v>
+        <v>-0.2151</v>
       </c>
       <c r="G8" t="n">
         <v>-0.8126</v>
@@ -1078,13 +1078,13 @@
         <v>1.5579</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7292999999999999</v>
+        <v>-0.2118</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9423</v>
+        <v>-0.0544</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.213</v>
+        <v>-0.1574</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1752</v>
+        <v>-0.8027</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9931</v>
+        <v>-1.7319</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8179</v>
+        <v>0.9292</v>
       </c>
       <c r="G9" t="n">
         <v>-1.8029</v>
@@ -1156,13 +1156,13 @@
         <v>1.5579</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2876</v>
+        <v>0.0849</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2446</v>
+        <v>0.0166</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.043</v>
+        <v>0.0683</v>
       </c>
       <c r="V9" t="n">
         <v>0.3311</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1301</v>
+        <v>-1.6974</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2439</v>
+        <v>-1.7833</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1138</v>
+        <v>0.0859</v>
       </c>
       <c r="G10" t="n">
         <v>-4.9294</v>
@@ -1234,13 +1234,13 @@
         <v>1.3632</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5317</v>
+        <v>-0.099</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3775</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1542</v>
+        <v>-0.1821</v>
       </c>
       <c r="V10" t="n">
         <v>2.1626</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.0367</v>
+        <v>-4.7306</v>
       </c>
       <c r="E11" t="n">
         <v>-3.6421</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3946</v>
+        <v>-1.0885</v>
       </c>
       <c r="G11" t="n">
         <v>-2.0197</v>
@@ -1312,13 +1312,13 @@
         <v>0.5842000000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4854</v>
+        <v>-0.1793</v>
       </c>
       <c r="T11" t="n">
         <v>-0.2012</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2842</v>
+        <v>0.0219</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.4506</v>
+        <v>-5.3464</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.7812</v>
+        <v>-2.4822</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.6694</v>
+        <v>-2.8642</v>
       </c>
       <c r="G12" t="n">
         <v>-2.0058</v>
@@ -1390,13 +1390,13 @@
         <v>1.7526</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2628</v>
+        <v>-0.1585</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8103</v>
+        <v>-0.5113</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5475</v>
+        <v>0.3528</v>
       </c>
       <c r="V12" t="n">
         <v>-3.7663</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1723000000000017</v>
+        <v>0.4813999999999989</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.5354</v>
+        <v>-1.226200000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7077</v>
+        <v>1.707599999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-1.690699999999999</v>
@@ -1468,13 +1468,13 @@
         <v>10.7105</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4013000000000002</v>
+        <v>0.7105999999999998</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.5182</v>
+        <v>-1.2089</v>
       </c>
       <c r="U13" t="n">
-        <v>1.9195</v>
+        <v>1.9196</v>
       </c>
       <c r="V13" t="n">
         <v>-0.4858000000000002</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.974</v>
+        <v>7.0999</v>
       </c>
       <c r="E14" t="n">
-        <v>5.9149</v>
+        <v>6.4133</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0591</v>
+        <v>0.6866</v>
       </c>
       <c r="G14" t="n">
         <v>5.3081</v>
@@ -1546,13 +1546,13 @@
         <v>1.1684</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.1931</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6959</v>
+        <v>-0.1975</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4972</v>
+        <v>0.1303</v>
       </c>
       <c r="V14" t="n">
         <v>3.6116</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.967</v>
+        <v>4.3317</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1334</v>
+        <v>3.5321</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8336</v>
+        <v>0.7995</v>
       </c>
       <c r="G15" t="n">
         <v>3.7808</v>
@@ -1624,13 +1624,13 @@
         <v>1.5579</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1609</v>
+        <v>0.5256</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4485</v>
+        <v>-0.0498</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6095</v>
+        <v>0.5754</v>
       </c>
       <c r="V15" t="n">
         <v>-0.5590000000000001</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X. ELVIRA GOMEZ</t>
+          <t>T. WRIGHT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2973</v>
+        <v>1.3985</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2828</v>
+        <v>0.6532</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0144</v>
+        <v>0.7453</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2857</v>
+        <v>1.4164</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9724</v>
+        <v>0.47</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.2581</v>
+        <v>0.9464</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3562</v>
+        <v>0.8729</v>
       </c>
       <c r="K16" t="n">
-        <v>1.442</v>
+        <v>0.7108</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.0859</v>
+        <v>0.1621</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6419</v>
+        <v>0.5436</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4696</v>
+        <v>-0.2407</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1723</v>
+        <v>0.7843</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.7789</v>
+        <v>0.7789</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9474</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1684</v>
+        <v>0.7789</v>
       </c>
       <c r="S16" t="n">
-        <v>2.9209</v>
+        <v>-0.2379</v>
       </c>
       <c r="T16" t="n">
-        <v>2.874</v>
+        <v>-0.2196</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0469</v>
+        <v>-0.0182</v>
       </c>
       <c r="V16" t="n">
         <v>-0.5590000000000001</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. WRIGHT</t>
+          <t>V. VINOS ALTEMIR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0617</v>
+        <v>0.7987</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2545</v>
+        <v>-0.5665</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8072</v>
+        <v>1.3651</v>
       </c>
       <c r="G17" t="n">
-        <v>1.4164</v>
+        <v>1.5282</v>
       </c>
       <c r="H17" t="n">
-        <v>0.47</v>
+        <v>-0.0344</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9464</v>
+        <v>1.5626</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8729</v>
+        <v>1.2452</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7108</v>
+        <v>-0.6029</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1621</v>
+        <v>1.8481</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5436</v>
+        <v>0.283</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2407</v>
+        <v>0.5685</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7843</v>
+        <v>-0.2855</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7789</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7789</v>
+        <v>0.9737</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5747</v>
+        <v>-0.7296</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6183</v>
+        <v>-0.838</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0436</v>
+        <v>0.1084</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.5590000000000001</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5590000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8444</v>
+        <v>0.7052</v>
       </c>
       <c r="E18" t="n">
         <v>-0.0083</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8527</v>
+        <v>0.7136</v>
       </c>
       <c r="G18" t="n">
         <v>-0.9655</v>
@@ -1858,13 +1858,13 @@
         <v>0.7789</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4204</v>
+        <v>0.2813</v>
       </c>
       <c r="T18" t="n">
         <v>-0.3867</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8071</v>
+        <v>0.6679</v>
       </c>
       <c r="V18" t="n">
         <v>0.6105</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>V. VINOS ALTEMIR</t>
+          <t>O. STUMER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1217</v>
+        <v>0.1061</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9651999999999999</v>
+        <v>-0.0416</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0869</v>
+        <v>0.1477</v>
       </c>
       <c r="G19" t="n">
-        <v>1.5282</v>
+        <v>0.1308</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0344</v>
+        <v>-0.4008</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5626</v>
+        <v>0.5316</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2452</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6029</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>1.8481</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.283</v>
+        <v>0.0487</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5685</v>
+        <v>-0.4829</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2855</v>
+        <v>0.5316</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9737</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9737</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.4065</v>
+        <v>-0.0247</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.2367</v>
+        <v>-0.1237</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1698</v>
+        <v>0.099</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O. STUMER</t>
+          <t>E. IBAEZ ALDAZABAL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.033</v>
+        <v>-0.5803</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0416</v>
+        <v>-0.7338</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0086</v>
+        <v>0.1535</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1308</v>
+        <v>-0.4371</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4008</v>
+        <v>0.3263</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5316</v>
+        <v>-0.7634</v>
       </c>
       <c r="J20" t="n">
-        <v>0.08210000000000001</v>
+        <v>-0.624</v>
       </c>
       <c r="K20" t="n">
-        <v>0.08210000000000001</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-0.624</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0487</v>
+        <v>0.1869</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4829</v>
+        <v>0.3263</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5316</v>
+        <v>-0.1395</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.3895</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.3895</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1638</v>
+        <v>0.0263</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1237</v>
+        <v>-0.1098</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0401</v>
+        <v>0.1361</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. IBAEZ ALDAZABAL</t>
+          <t>X. ELVIRA GOMEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6127</v>
+        <v>-0.6855</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9332</v>
+        <v>-0.91</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3205</v>
+        <v>0.2246</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4371</v>
+        <v>-0.2857</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3263</v>
+        <v>0.9724</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7634</v>
+        <v>-1.2581</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.624</v>
+        <v>0.3562</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1.442</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.624</v>
+        <v>-1.0859</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1869</v>
+        <v>-0.6419</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3263</v>
+        <v>-0.4696</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1395</v>
+        <v>-0.1723</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3895</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.9474</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3895</v>
+        <v>1.1684</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0061</v>
+        <v>0.9381</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3092</v>
+        <v>0.6811</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3031</v>
+        <v>0.257</v>
       </c>
       <c r="V21" t="n">
         <v>-0.5590000000000001</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0354</v>
+        <v>-2.9071</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.4508</v>
+        <v>-3.6502</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4154</v>
+        <v>0.7431</v>
       </c>
       <c r="G22" t="n">
         <v>-1.8113</v>
@@ -2170,13 +2170,13 @@
         <v>0.7789</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0557</v>
+        <v>0.0727</v>
       </c>
       <c r="T22" t="n">
-        <v>0.216</v>
+        <v>0.0166</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2716</v>
+        <v>0.056</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.7424</v>
+        <v>-3.9434</v>
       </c>
       <c r="E23" t="n">
         <v>-2.1355</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6069</v>
+        <v>-1.8079</v>
       </c>
       <c r="G23" t="n">
         <v>-2.475</v>
@@ -2248,13 +2248,13 @@
         <v>0.3895</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5379</v>
+        <v>0.3369</v>
       </c>
       <c r="T23" t="n">
         <v>-0.0775</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6153999999999999</v>
+        <v>0.4144</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2211</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.0148</v>
+        <v>-5.1671</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.7588</v>
+        <v>-4.2605</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.2559</v>
+        <v>-0.9067</v>
       </c>
       <c r="G24" t="n">
         <v>-4.4989</v>
@@ -2326,13 +2326,13 @@
         <v>0.7789</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0417</v>
+        <v>-0.194</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.113</v>
+        <v>-0.6146</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0713</v>
+        <v>0.4206</v>
       </c>
       <c r="V24" t="n">
         <v>-0.2795</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1721999999999992</v>
+        <v>1.156700000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.707799999999998</v>
+        <v>-1.7078</v>
       </c>
       <c r="F25" t="n">
-        <v>1.535600000000001</v>
+        <v>2.8644</v>
       </c>
       <c r="G25" t="n">
         <v>1.6908</v>
@@ -2377,7 +2377,7 @@
         <v>-1.9935</v>
       </c>
       <c r="J25" t="n">
-        <v>6.472400000000001</v>
+        <v>6.472399999999999</v>
       </c>
       <c r="K25" t="n">
         <v>7.5389</v>
@@ -2404,16 +2404,16 @@
         <v>8.763</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4015000000000001</v>
+        <v>0.9276</v>
       </c>
       <c r="T25" t="n">
         <v>-1.9195</v>
       </c>
       <c r="U25" t="n">
-        <v>1.5182</v>
+        <v>2.8469</v>
       </c>
       <c r="V25" t="n">
-        <v>0.4854999999999999</v>
+        <v>0.4854999999999997</v>
       </c>
       <c r="W25" t="n">
         <v>4.450099999999999</v>
